--- a/tabtools/demo/effecttab.xlsx
+++ b/tabtools/demo/effecttab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="170" uniqueCount="52">
   <si>
     <t>Table 3. Treatment Effects</t>
   </si>
@@ -86,1454 +86,3298 @@
   <si>
     <t>0.30</t>
   </si>
+  <si>
+    <t>Age (years)</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>var(bmi)</t>
+  </si>
+  <si>
+    <t>var(_cons)</t>
+  </si>
+  <si>
+    <t>var(e)</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>(0.01, 0.02)</t>
+  </si>
+  <si>
+    <t>(-0.02, 0.17)</t>
+  </si>
+  <si>
+    <t>(0.01, 0.06)</t>
+  </si>
+  <si>
+    <t>(0.00,  2.6e+43)</t>
+  </si>
+  <si>
+    <t>(0.21, 0.29)</t>
+  </si>
+  <si>
+    <t>(2.58, 3.51)</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>3.20</t>
+  </si>
+  <si>
+    <t>(0.02, 0.28)</t>
+  </si>
+  <si>
+    <t>(0.05, 0.16)</t>
+  </si>
+  <si>
+    <t>(0.23, 1.86)</t>
+  </si>
+  <si>
+    <t>(0.21, 0.27)</t>
+  </si>
+  <si>
+    <t>(2.70, 3.71)</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="379">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="787">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1745,7 +3589,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="285">
+  <borders count="589">
     <border>
       <left/>
       <right/>
@@ -3681,11 +5525,2079 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="589">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -4790,6 +8702,1192 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="378" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" xfId="0"/>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="437" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="438" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="439" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="440" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="441" xfId="0"/>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="676" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="678" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="680" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="682" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="686" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="688" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="690" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="692" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="694" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="696" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="698" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="700" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="702" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="704" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="706" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="708" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="710" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="714" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="722" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="728" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="730" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4802,149 +9900,166 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" style="144" customWidth="true"/>
-    <col min="3" max="3" width="5.9375" style="145" customWidth="true"/>
-    <col min="4" max="4" width="13.0625" style="146" customWidth="true"/>
-    <col min="5" max="5" width="9.0234375" style="147" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" style="438" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="439" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="440" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="441" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="143" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="245" t="s">
+    <row r="1" s="437" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="544" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="246" t="s">
+      <c r="B1" s="545" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="247" t="s">
+      <c r="C1" s="546" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="248" t="s">
+      <c r="D1" s="547" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="249" t="s">
+      <c r="E1" s="548" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="250" t="s">
+      <c r="A2" s="549" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="550" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="551" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="253" t="s">
+      <c r="D2" s="552" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="254" t="s">
+      <c r="E2" s="553" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="255" t="s">
+      <c r="A3" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="555" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="556" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="258" t="s">
+      <c r="D3" s="557" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="259" t="s">
+      <c r="E3" s="558" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="260" t="s">
+      <c r="A4" s="559" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="261" t="s">
-        <v>2</v>
+      <c r="B4" s="560" t="s">
+        <v>24</v>
       </c>
-      <c r="C4" s="262" t="s">
-        <v>8</v>
+      <c r="C4" s="561" t="s">
+        <v>31</v>
       </c>
-      <c r="D4" s="263" t="s">
-        <v>14</v>
+      <c r="D4" s="562" t="s">
+        <v>35</v>
       </c>
-      <c r="E4" s="264" t="s">
-        <v>20</v>
+      <c r="E4" s="563" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="265" t="s">
+      <c r="A5" s="564" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="266" t="s">
-        <v>3</v>
+      <c r="B5" s="565" t="s">
+        <v>25</v>
       </c>
-      <c r="C5" s="267" t="s">
-        <v>9</v>
+      <c r="C5" s="566" t="s">
+        <v>42</v>
       </c>
-      <c r="D5" s="268" t="s">
-        <v>15</v>
+      <c r="D5" s="567" t="s">
+        <v>46</v>
       </c>
-      <c r="E5" s="269" t="s">
-        <v>21</v>
+      <c r="E5" s="568" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="270" t="s">
+      <c r="A6" s="569" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="271" t="s">
-        <v>4</v>
+      <c r="B6" s="570" t="s">
+        <v>26</v>
       </c>
-      <c r="C6" s="272" t="s">
-        <v>10</v>
+      <c r="C6" s="571" t="s">
+        <v>43</v>
       </c>
-      <c r="D6" s="273" t="s">
-        <v>16</v>
+      <c r="D6" s="572" t="s">
+        <v>47</v>
       </c>
-      <c r="E6" s="274" t="s">
-        <v>22</v>
+      <c r="E6" s="573" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="275" t="s">
+      <c r="A7" s="574" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="276" t="s">
-        <v>5</v>
+      <c r="B7" s="575" t="s">
+        <v>27</v>
       </c>
-      <c r="C7" s="277" t="s">
-        <v>11</v>
+      <c r="C7" s="576" t="s">
+        <v>44</v>
       </c>
-      <c r="D7" s="278" t="s">
-        <v>17</v>
+      <c r="D7" s="577" t="s">
+        <v>48</v>
       </c>
-      <c r="E7" s="279" t="s">
-        <v>21</v>
+      <c r="E7" s="578" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="280" t="s">
+      <c r="A8" s="579" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="281" t="s">
+      <c r="B8" s="580" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="581" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="582" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="583" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="584" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="585" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="282" t="s">
-        <v>12</v>
+      <c r="C9" s="586" t="s">
+        <v>45</v>
       </c>
-      <c r="D8" s="283" t="s">
-        <v>18</v>
+      <c r="D9" s="587" t="s">
+        <v>50</v>
       </c>
-      <c r="E8" s="284" t="s">
-        <v>23</v>
+      <c r="E9" s="588" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/tabtools/demo/effecttab.xlsx
+++ b/tabtools/demo/effecttab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="170" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="215" uniqueCount="52">
   <si>
     <t>Table 3. Treatment Effects</t>
   </si>
@@ -175,1449 +175,2329 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="787">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="991">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -3589,7 +4469,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="589">
+  <borders count="741">
     <border>
       <left/>
       <right/>
@@ -7593,11 +8473,1045 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="589">
+  <cellXfs count="741">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -9888,6 +11802,599 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="786" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="589" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="590" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="591" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="592" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="593" xfId="0"/>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="817" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="846" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="848" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="862" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="866" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9903,162 +12410,162 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" style="438" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="439" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="440" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="441" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" style="590" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="591" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="592" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="593" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="437" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="544" t="s">
+    <row r="1" s="589" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="696" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="545" t="s">
+      <c r="B1" s="697" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="546" t="s">
+      <c r="C1" s="698" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="547" t="s">
+      <c r="D1" s="699" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="548" t="s">
+      <c r="E1" s="700" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="549" t="s">
+      <c r="A2" s="701" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="550" t="s">
+      <c r="B2" s="702" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="551" t="s">
+      <c r="C2" s="703" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="552" t="s">
+      <c r="D2" s="704" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="553" t="s">
+      <c r="E2" s="705" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="554" t="s">
+      <c r="A3" s="706" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="555" t="s">
+      <c r="B3" s="707" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="556" t="s">
+      <c r="C3" s="708" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="557" t="s">
+      <c r="D3" s="709" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="558" t="s">
+      <c r="E3" s="710" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="559" t="s">
+      <c r="A4" s="711" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="560" t="s">
+      <c r="B4" s="712" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="561" t="s">
+      <c r="C4" s="713" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="562" t="s">
+      <c r="D4" s="714" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="563" t="s">
+      <c r="E4" s="715" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="564" t="s">
+      <c r="A5" s="716" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="565" t="s">
+      <c r="B5" s="717" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="566" t="s">
+      <c r="C5" s="718" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="567" t="s">
+      <c r="D5" s="719" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="568" t="s">
+      <c r="E5" s="720" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="569" t="s">
+      <c r="A6" s="721" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="570" t="s">
+      <c r="B6" s="722" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="571" t="s">
+      <c r="C6" s="723" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="572" t="s">
+      <c r="D6" s="724" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="573" t="s">
+      <c r="E6" s="725" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="574" t="s">
+      <c r="A7" s="726" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="575" t="s">
+      <c r="B7" s="727" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="576" t="s">
+      <c r="C7" s="728" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="577" t="s">
+      <c r="D7" s="729" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="578" t="s">
+      <c r="E7" s="730" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="579" t="s">
+      <c r="A8" s="731" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="580" t="s">
+      <c r="B8" s="732" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="581" t="s">
+      <c r="C8" s="733" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="582" t="s">
+      <c r="D8" s="734" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="583" t="s">
+      <c r="E8" s="735" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="584" t="s">
+      <c r="A9" s="736" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="585" t="s">
+      <c r="B9" s="737" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="586" t="s">
+      <c r="C9" s="738" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="587" t="s">
+      <c r="D9" s="739" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="588" t="s">
+      <c r="E9" s="740" t="s">
         <v>21</v>
       </c>
     </row>

--- a/tabtools/demo/effecttab.xlsx
+++ b/tabtools/demo/effecttab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="215" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="52">
   <si>
     <t>Table 3. Treatment Effects</t>
   </si>
@@ -175,1449 +175,2329 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="991">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="1195">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -4469,7 +5349,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="741">
+  <borders count="893">
     <border>
       <left/>
       <right/>
@@ -9507,11 +10387,1045 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="741">
+  <cellXfs count="893">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -12395,6 +14309,599 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="990" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="741" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="742" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="743" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="744" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="745" xfId="0"/>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1095" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1097" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1099" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1101" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1103" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1152" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1154" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1156" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1158" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1160" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1162" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1164" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1166" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1168" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1170" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1172" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1174" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1176" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1178" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1180" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1182" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1184" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1186" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1188" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1190" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1192" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1194" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12410,162 +14917,162 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" style="590" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="591" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="592" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="593" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" style="742" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="743" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="744" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="745" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="589" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="696" t="s">
+    <row r="1" s="741" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="848" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="697" t="s">
+      <c r="B1" s="849" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="698" t="s">
+      <c r="C1" s="850" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="699" t="s">
+      <c r="D1" s="851" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="700" t="s">
+      <c r="E1" s="852" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="701" t="s">
+      <c r="A2" s="853" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="702" t="s">
+      <c r="B2" s="854" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="703" t="s">
+      <c r="C2" s="855" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="704" t="s">
+      <c r="D2" s="856" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="705" t="s">
+      <c r="E2" s="857" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="706" t="s">
+      <c r="A3" s="858" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="707" t="s">
+      <c r="B3" s="859" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="708" t="s">
+      <c r="C3" s="860" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="709" t="s">
+      <c r="D3" s="861" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="710" t="s">
+      <c r="E3" s="862" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="711" t="s">
+      <c r="A4" s="863" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="712" t="s">
+      <c r="B4" s="864" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="713" t="s">
+      <c r="C4" s="865" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="714" t="s">
+      <c r="D4" s="866" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="715" t="s">
+      <c r="E4" s="867" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="716" t="s">
+      <c r="A5" s="868" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="717" t="s">
+      <c r="B5" s="869" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="718" t="s">
+      <c r="C5" s="870" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="719" t="s">
+      <c r="D5" s="871" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="720" t="s">
+      <c r="E5" s="872" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="721" t="s">
+      <c r="A6" s="873" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="722" t="s">
+      <c r="B6" s="874" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="723" t="s">
+      <c r="C6" s="875" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="724" t="s">
+      <c r="D6" s="876" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="725" t="s">
+      <c r="E6" s="877" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="726" t="s">
+      <c r="A7" s="878" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="727" t="s">
+      <c r="B7" s="879" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="728" t="s">
+      <c r="C7" s="880" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="729" t="s">
+      <c r="D7" s="881" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="730" t="s">
+      <c r="E7" s="882" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="731" t="s">
+      <c r="A8" s="883" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="732" t="s">
+      <c r="B8" s="884" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="733" t="s">
+      <c r="C8" s="885" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="734" t="s">
+      <c r="D8" s="886" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="735" t="s">
+      <c r="E8" s="887" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="736" t="s">
+      <c r="A9" s="888" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="737" t="s">
+      <c r="B9" s="889" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="738" t="s">
+      <c r="C9" s="890" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="739" t="s">
+      <c r="D9" s="891" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="740" t="s">
+      <c r="E9" s="892" t="s">
         <v>21</v>
       </c>
     </row>
